--- a/content/post/drafts/season-prediction/klaebo.xlsx
+++ b/content/post/drafts/season-prediction/klaebo.xlsx
@@ -17,10 +17,10 @@
     <t xml:space="preserve">Skier</t>
   </si>
   <si>
-    <t xml:space="preserve">Klaebo_With_TDS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klaebo_Without_TDS</t>
+    <t xml:space="preserve">Klaebo with TDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klaebo without TDS</t>
   </si>
   <si>
     <t xml:space="preserve">Harald Østberg Amundsen</t>
@@ -47,12 +47,12 @@
     <t xml:space="preserve">Calle Halfvarsson</t>
   </si>
   <si>
+    <t xml:space="preserve">Didrik Tønseth</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gus Schumacher</t>
   </si>
   <si>
-    <t xml:space="preserve">Didrik Tønseth</t>
-  </si>
-  <si>
     <t xml:space="preserve">William Poromaa</t>
   </si>
   <si>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">Jens Burman</t>
   </si>
   <si>
+    <t xml:space="preserve">Johan Häggström</t>
+  </si>
+  <si>
     <t xml:space="preserve">Edvin Anger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johan Häggström</t>
   </si>
   <si>
     <t xml:space="preserve">Even Northug</t>
@@ -474,7 +474,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
